--- a/5/search/FY3_Missile1_results/best_solution.xlsx
+++ b/5/search/FY3_Missile1_results/best_solution.xlsx
@@ -487,34 +487,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90</v>
+        <v>76.5</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6000</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="F2" t="n">
-        <v>-312</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6000</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="J2" t="n">
-        <v>621.6</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
